--- a/Backup_Database/2026-09-21/MK_Mill_Plant_Operations_Report_2026-09-21.xlsx
+++ b/Backup_Database/2026-09-21/MK_Mill_Plant_Operations_Report_2026-09-21.xlsx
@@ -445,7 +445,7 @@
         <v>Generated At:</v>
       </c>
       <c r="D6" t="str">
-        <v>21/9/2026, 7:20:46 pm</v>
+        <v>21/9/2026, 7:39:59 pm</v>
       </c>
     </row>
     <row r="7">
